--- a/Templates/nvr.xlsx
+++ b/Templates/nvr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50d76e1b4061cd6b/Thales/Dell Laptop/Makkah/MTR/MTR-RTR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50d76e1b4061cd6b/Thales/GIT/foreman/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="8_{DF5CBC03-C4A3-4EDA-B31B-7F829A74A012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{603A79FE-96A4-4465-A864-BB98EA95466E}"/>
+  <xr:revisionPtr revIDLastSave="555" documentId="8_{DF5CBC03-C4A3-4EDA-B31B-7F829A74A012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AF82149-E558-4C27-A714-B52ACD3AC19D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{820893D6-3695-45FD-9383-EBE0667016CA}"/>
   </bookViews>
@@ -3773,7 +3773,7 @@
         <v>1007</v>
       </c>
       <c r="Q2" s="4" t="str">
-        <f>_xlfn.CONCAT(A2:B2,D2:H2)</f>
+        <f t="shared" ref="Q2:Q9" si="0">_xlfn.CONCAT(A2:B2,D2:H2)</f>
         <v>tvsnvrpic001mp</v>
       </c>
       <c r="R2" s="8" t="s">
@@ -3783,8 +3783,8 @@
         <v>728</v>
       </c>
       <c r="T2" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S2,"/mtr-rec/",O2)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f>_xlfn.CONCAT("/ifs/",S2,"/mtr-rec/",P2)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -3837,7 +3837,7 @@
         <v>1007</v>
       </c>
       <c r="Q3" s="4" t="str">
-        <f>_xlfn.CONCAT(A3:B3,D3:H3)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic002mp</v>
       </c>
       <c r="R3" s="8" t="s">
@@ -3847,8 +3847,8 @@
         <v>728</v>
       </c>
       <c r="T3" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S3,"/mtr-rec/",O3)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" ref="T3:T8" si="1">_xlfn.CONCAT("/ifs/",S3,"/mtr-rec/",P3)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -3901,7 +3901,7 @@
         <v>1007</v>
       </c>
       <c r="Q4" s="4" t="str">
-        <f>_xlfn.CONCAT(A4:B4,D4:H4)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic003mp</v>
       </c>
       <c r="R4" s="8" t="s">
@@ -3911,8 +3911,8 @@
         <v>728</v>
       </c>
       <c r="T4" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S4,"/mtr-rec/",O4)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" si="1"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>1007</v>
       </c>
       <c r="Q5" s="4" t="str">
-        <f>_xlfn.CONCAT(A5:B5,D5:H5)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic004mp</v>
       </c>
       <c r="R5" s="8" t="s">
@@ -3975,8 +3975,8 @@
         <v>728</v>
       </c>
       <c r="T5" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S5,"/mtr-rec/",O5)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" si="1"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4029,7 +4029,7 @@
         <v>1007</v>
       </c>
       <c r="Q6" s="4" t="str">
-        <f>_xlfn.CONCAT(A6:B6,D6:H6)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic005mp</v>
       </c>
       <c r="R6" s="8" t="s">
@@ -4039,8 +4039,8 @@
         <v>728</v>
       </c>
       <c r="T6" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S6,"/mtr-rec/",O6)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" si="1"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>1007</v>
       </c>
       <c r="Q7" s="4" t="str">
-        <f>_xlfn.CONCAT(A7:B7,D7:H7)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic006mp</v>
       </c>
       <c r="R7" s="8" t="s">
@@ -4103,8 +4103,8 @@
         <v>728</v>
       </c>
       <c r="T7" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S7,"/mtr-rec/",O7)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" si="1"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>1007</v>
       </c>
       <c r="Q8" s="4" t="str">
-        <f>_xlfn.CONCAT(A8:B8,D8:H8)</f>
+        <f t="shared" si="0"/>
         <v>tvsnvrpic007mp</v>
       </c>
       <c r="R8" s="8" t="s">
@@ -4167,8 +4167,8 @@
         <v>728</v>
       </c>
       <c r="T8" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S8,"/mtr-rec/",O8)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu000mp</v>
+        <f t="shared" si="1"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm000</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
         <v>1007</v>
       </c>
       <c r="Q9" s="4" t="str">
-        <f>_xlfn.CONCAT(A9:B9,D9:H9)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="R9" s="8"/>
@@ -4271,8 +4271,8 @@
         <v>728</v>
       </c>
       <c r="T10" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S10,"/mtr-rec/",O10)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f>_xlfn.CONCAT("/ifs/",S10,"/mtr-rec/",P10)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4334,8 +4334,8 @@
         <v>728</v>
       </c>
       <c r="T11" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S11,"/mtr-rec/",O11)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" ref="T11:T16" si="2">_xlfn.CONCAT("/ifs/",S11,"/mtr-rec/",P11)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4397,8 +4397,8 @@
         <v>728</v>
       </c>
       <c r="T12" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S12,"/mtr-rec/",O12)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" si="2"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4460,8 +4460,8 @@
         <v>728</v>
       </c>
       <c r="T13" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S13,"/mtr-rec/",O13)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" si="2"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4523,8 +4523,8 @@
         <v>728</v>
       </c>
       <c r="T14" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S14,"/mtr-rec/",O14)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" si="2"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4586,8 +4586,8 @@
         <v>728</v>
       </c>
       <c r="T15" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S15,"/mtr-rec/",O15)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" si="2"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4649,8 +4649,8 @@
         <v>728</v>
       </c>
       <c r="T16" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S16,"/mtr-rec/",O16)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu010mp</v>
+        <f t="shared" si="2"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm010</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4753,8 +4753,8 @@
         <v>728</v>
       </c>
       <c r="T18" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S18,"/mtr-rec/",O18)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f>_xlfn.CONCAT("/ifs/",S18,"/mtr-rec/",P18)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4816,8 +4816,8 @@
         <v>728</v>
       </c>
       <c r="T19" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S19,"/mtr-rec/",O19)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" ref="T19:T24" si="3">_xlfn.CONCAT("/ifs/",S19,"/mtr-rec/",P19)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4879,8 +4879,8 @@
         <v>728</v>
       </c>
       <c r="T20" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S20,"/mtr-rec/",O20)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" si="3"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -4942,8 +4942,8 @@
         <v>728</v>
       </c>
       <c r="T21" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S21,"/mtr-rec/",O21)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" si="3"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5005,8 +5005,8 @@
         <v>728</v>
       </c>
       <c r="T22" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S22,"/mtr-rec/",O22)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" si="3"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5068,8 +5068,8 @@
         <v>728</v>
       </c>
       <c r="T23" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S23,"/mtr-rec/",O23)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" si="3"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5131,8 +5131,8 @@
         <v>728</v>
       </c>
       <c r="T24" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S24,"/mtr-rec/",O24)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu020mp</v>
+        <f t="shared" si="3"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm020</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5235,8 +5235,8 @@
         <v>728</v>
       </c>
       <c r="T26" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S26,"/mtr-rec/",O26)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f>_xlfn.CONCAT("/ifs/",S26,"/mtr-rec/",P26)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5298,8 +5298,8 @@
         <v>728</v>
       </c>
       <c r="T27" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S27,"/mtr-rec/",O27)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" ref="T27:T90" si="4">_xlfn.CONCAT("/ifs/",S27,"/mtr-rec/",P27)</f>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5361,8 +5361,8 @@
         <v>728</v>
       </c>
       <c r="T28" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S28,"/mtr-rec/",O28)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5424,8 +5424,8 @@
         <v>728</v>
       </c>
       <c r="T29" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S29,"/mtr-rec/",O29)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5487,8 +5487,8 @@
         <v>728</v>
       </c>
       <c r="T30" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S30,"/mtr-rec/",O30)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5550,8 +5550,8 @@
         <v>728</v>
       </c>
       <c r="T31" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S31,"/mtr-rec/",O31)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5613,8 +5613,8 @@
         <v>728</v>
       </c>
       <c r="T32" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S32,"/mtr-rec/",O32)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu030mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm030</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5651,7 +5651,7 @@
         <v>1010</v>
       </c>
       <c r="Q33" s="4" t="str">
-        <f>_xlfn.CONCAT(A33:B33,D33:H33)</f>
+        <f t="shared" ref="Q33:Q64" si="5">_xlfn.CONCAT(A33:B33,D33:H33)</f>
         <v/>
       </c>
       <c r="R33" s="8"/>
@@ -5708,7 +5708,7 @@
         <v>1011</v>
       </c>
       <c r="Q34" s="4" t="str">
-        <f>_xlfn.CONCAT(A34:B34,D34:H34)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic041mp</v>
       </c>
       <c r="R34" s="8" t="s">
@@ -5718,8 +5718,8 @@
         <v>728</v>
       </c>
       <c r="T34" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S34,"/mtr-rec/",O34)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5772,7 +5772,7 @@
         <v>1011</v>
       </c>
       <c r="Q35" s="4" t="str">
-        <f>_xlfn.CONCAT(A35:B35,D35:H35)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic042mp</v>
       </c>
       <c r="R35" s="8" t="s">
@@ -5782,8 +5782,8 @@
         <v>728</v>
       </c>
       <c r="T35" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S35,"/mtr-rec/",O35)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5836,7 +5836,7 @@
         <v>1011</v>
       </c>
       <c r="Q36" s="4" t="str">
-        <f>_xlfn.CONCAT(A36:B36,D36:H36)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic043mp</v>
       </c>
       <c r="R36" s="8" t="s">
@@ -5846,8 +5846,8 @@
         <v>728</v>
       </c>
       <c r="T36" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S36,"/mtr-rec/",O36)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
         <v>1011</v>
       </c>
       <c r="Q37" s="4" t="str">
-        <f>_xlfn.CONCAT(A37:B37,D37:H37)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic044mp</v>
       </c>
       <c r="R37" s="8" t="s">
@@ -5910,8 +5910,8 @@
         <v>728</v>
       </c>
       <c r="T37" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S37,"/mtr-rec/",O37)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -5964,7 +5964,7 @@
         <v>1011</v>
       </c>
       <c r="Q38" s="4" t="str">
-        <f>_xlfn.CONCAT(A38:B38,D38:H38)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic045mp</v>
       </c>
       <c r="R38" s="8" t="s">
@@ -5974,8 +5974,8 @@
         <v>728</v>
       </c>
       <c r="T38" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S38,"/mtr-rec/",O38)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6028,7 +6028,7 @@
         <v>1011</v>
       </c>
       <c r="Q39" s="4" t="str">
-        <f>_xlfn.CONCAT(A39:B39,D39:H39)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic046mp</v>
       </c>
       <c r="R39" s="8" t="s">
@@ -6038,8 +6038,8 @@
         <v>728</v>
       </c>
       <c r="T39" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S39,"/mtr-rec/",O39)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6092,7 +6092,7 @@
         <v>1011</v>
       </c>
       <c r="Q40" s="4" t="str">
-        <f>_xlfn.CONCAT(A40:B40,D40:H40)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic047mp</v>
       </c>
       <c r="R40" s="8" t="s">
@@ -6102,8 +6102,8 @@
         <v>728</v>
       </c>
       <c r="T40" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S40,"/mtr-rec/",O40)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu040mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm040</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6140,7 +6140,7 @@
         <v>1011</v>
       </c>
       <c r="Q41" s="4" t="str">
-        <f>_xlfn.CONCAT(A41:B41,D41:H41)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R41" s="8"/>
@@ -6197,7 +6197,7 @@
         <v>1012</v>
       </c>
       <c r="Q42" s="4" t="str">
-        <f>_xlfn.CONCAT(A42:B42,D42:H42)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic051mp</v>
       </c>
       <c r="R42" s="8" t="s">
@@ -6207,8 +6207,8 @@
         <v>728</v>
       </c>
       <c r="T42" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S42,"/mtr-rec/",O42)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6261,7 +6261,7 @@
         <v>1012</v>
       </c>
       <c r="Q43" s="4" t="str">
-        <f>_xlfn.CONCAT(A43:B43,D43:H43)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic052mp</v>
       </c>
       <c r="R43" s="8" t="s">
@@ -6271,8 +6271,8 @@
         <v>728</v>
       </c>
       <c r="T43" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S43,"/mtr-rec/",O43)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
         <v>1012</v>
       </c>
       <c r="Q44" s="4" t="str">
-        <f>_xlfn.CONCAT(A44:B44,D44:H44)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic053mp</v>
       </c>
       <c r="R44" s="8" t="s">
@@ -6335,8 +6335,8 @@
         <v>728</v>
       </c>
       <c r="T44" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S44,"/mtr-rec/",O44)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6389,7 +6389,7 @@
         <v>1012</v>
       </c>
       <c r="Q45" s="4" t="str">
-        <f>_xlfn.CONCAT(A45:B45,D45:H45)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic054mp</v>
       </c>
       <c r="R45" s="8" t="s">
@@ -6399,8 +6399,8 @@
         <v>728</v>
       </c>
       <c r="T45" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S45,"/mtr-rec/",O45)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6453,7 +6453,7 @@
         <v>1012</v>
       </c>
       <c r="Q46" s="4" t="str">
-        <f>_xlfn.CONCAT(A46:B46,D46:H46)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic055mp</v>
       </c>
       <c r="R46" s="8" t="s">
@@ -6463,8 +6463,8 @@
         <v>728</v>
       </c>
       <c r="T46" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S46,"/mtr-rec/",O46)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6517,7 +6517,7 @@
         <v>1012</v>
       </c>
       <c r="Q47" s="4" t="str">
-        <f>_xlfn.CONCAT(A47:B47,D47:H47)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic056mp</v>
       </c>
       <c r="R47" s="8" t="s">
@@ -6527,8 +6527,8 @@
         <v>728</v>
       </c>
       <c r="T47" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S47,"/mtr-rec/",O47)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6581,7 +6581,7 @@
         <v>1012</v>
       </c>
       <c r="Q48" s="4" t="str">
-        <f>_xlfn.CONCAT(A48:B48,D48:H48)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic057mp</v>
       </c>
       <c r="R48" s="8" t="s">
@@ -6591,8 +6591,8 @@
         <v>728</v>
       </c>
       <c r="T48" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S48,"/mtr-rec/",O48)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu050mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm050</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6629,7 +6629,7 @@
         <v>1012</v>
       </c>
       <c r="Q49" s="4" t="str">
-        <f>_xlfn.CONCAT(A49:B49,D49:H49)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R49" s="8"/>
@@ -6686,7 +6686,7 @@
         <v>1013</v>
       </c>
       <c r="Q50" s="4" t="str">
-        <f>_xlfn.CONCAT(A50:B50,D50:H50)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic061mp</v>
       </c>
       <c r="R50" s="8" t="s">
@@ -6696,8 +6696,8 @@
         <v>728</v>
       </c>
       <c r="T50" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S50,"/mtr-rec/",O50)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6750,7 +6750,7 @@
         <v>1013</v>
       </c>
       <c r="Q51" s="4" t="str">
-        <f>_xlfn.CONCAT(A51:B51,D51:H51)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic062mp</v>
       </c>
       <c r="R51" s="8" t="s">
@@ -6760,8 +6760,8 @@
         <v>728</v>
       </c>
       <c r="T51" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S51,"/mtr-rec/",O51)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6814,7 +6814,7 @@
         <v>1013</v>
       </c>
       <c r="Q52" s="4" t="str">
-        <f>_xlfn.CONCAT(A52:B52,D52:H52)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic063mp</v>
       </c>
       <c r="R52" s="8" t="s">
@@ -6824,8 +6824,8 @@
         <v>728</v>
       </c>
       <c r="T52" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S52,"/mtr-rec/",O52)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6878,7 +6878,7 @@
         <v>1013</v>
       </c>
       <c r="Q53" s="4" t="str">
-        <f>_xlfn.CONCAT(A53:B53,D53:H53)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic064mp</v>
       </c>
       <c r="R53" s="8" t="s">
@@ -6888,8 +6888,8 @@
         <v>728</v>
       </c>
       <c r="T53" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S53,"/mtr-rec/",O53)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -6942,7 +6942,7 @@
         <v>1013</v>
       </c>
       <c r="Q54" s="4" t="str">
-        <f>_xlfn.CONCAT(A54:B54,D54:H54)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic065mp</v>
       </c>
       <c r="R54" s="8" t="s">
@@ -6952,8 +6952,8 @@
         <v>728</v>
       </c>
       <c r="T54" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S54,"/mtr-rec/",O54)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7006,7 +7006,7 @@
         <v>1013</v>
       </c>
       <c r="Q55" s="4" t="str">
-        <f>_xlfn.CONCAT(A55:B55,D55:H55)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic066mp</v>
       </c>
       <c r="R55" s="8" t="s">
@@ -7016,8 +7016,8 @@
         <v>728</v>
       </c>
       <c r="T55" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S55,"/mtr-rec/",O55)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7070,7 +7070,7 @@
         <v>1013</v>
       </c>
       <c r="Q56" s="4" t="str">
-        <f>_xlfn.CONCAT(A56:B56,D56:H56)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic067mp</v>
       </c>
       <c r="R56" s="8" t="s">
@@ -7080,8 +7080,8 @@
         <v>728</v>
       </c>
       <c r="T56" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S56,"/mtr-rec/",O56)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu060mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm060</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7118,7 +7118,7 @@
         <v>1013</v>
       </c>
       <c r="Q57" s="4" t="str">
-        <f>_xlfn.CONCAT(A57:B57,D57:H57)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R57" s="8"/>
@@ -7175,7 +7175,7 @@
         <v>1014</v>
       </c>
       <c r="Q58" s="4" t="str">
-        <f>_xlfn.CONCAT(A58:B58,D58:H58)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic071mp</v>
       </c>
       <c r="R58" s="8" t="s">
@@ -7185,8 +7185,8 @@
         <v>728</v>
       </c>
       <c r="T58" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S58,"/mtr-rec/",O58)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7239,7 +7239,7 @@
         <v>1014</v>
       </c>
       <c r="Q59" s="4" t="str">
-        <f>_xlfn.CONCAT(A59:B59,D59:H59)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic072mp</v>
       </c>
       <c r="R59" s="8" t="s">
@@ -7249,8 +7249,8 @@
         <v>728</v>
       </c>
       <c r="T59" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S59,"/mtr-rec/",O59)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7303,7 +7303,7 @@
         <v>1014</v>
       </c>
       <c r="Q60" s="4" t="str">
-        <f>_xlfn.CONCAT(A60:B60,D60:H60)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic073mp</v>
       </c>
       <c r="R60" s="8" t="s">
@@ -7313,8 +7313,8 @@
         <v>728</v>
       </c>
       <c r="T60" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S60,"/mtr-rec/",O60)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7367,7 +7367,7 @@
         <v>1014</v>
       </c>
       <c r="Q61" s="4" t="str">
-        <f>_xlfn.CONCAT(A61:B61,D61:H61)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic074mp</v>
       </c>
       <c r="R61" s="8" t="s">
@@ -7377,8 +7377,8 @@
         <v>728</v>
       </c>
       <c r="T61" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S61,"/mtr-rec/",O61)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7431,7 +7431,7 @@
         <v>1014</v>
       </c>
       <c r="Q62" s="4" t="str">
-        <f>_xlfn.CONCAT(A62:B62,D62:H62)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic075mp</v>
       </c>
       <c r="R62" s="8" t="s">
@@ -7441,8 +7441,8 @@
         <v>728</v>
       </c>
       <c r="T62" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S62,"/mtr-rec/",O62)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7495,7 +7495,7 @@
         <v>1014</v>
       </c>
       <c r="Q63" s="4" t="str">
-        <f>_xlfn.CONCAT(A63:B63,D63:H63)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic076mp</v>
       </c>
       <c r="R63" s="8" t="s">
@@ -7505,8 +7505,8 @@
         <v>728</v>
       </c>
       <c r="T63" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S63,"/mtr-rec/",O63)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7559,7 +7559,7 @@
         <v>1014</v>
       </c>
       <c r="Q64" s="4" t="str">
-        <f>_xlfn.CONCAT(A64:B64,D64:H64)</f>
+        <f t="shared" si="5"/>
         <v>tvsnvrpic077mp</v>
       </c>
       <c r="R64" s="8" t="s">
@@ -7569,8 +7569,8 @@
         <v>728</v>
       </c>
       <c r="T64" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S64,"/mtr-rec/",O64)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu070mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm070</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7607,7 +7607,7 @@
         <v>1014</v>
       </c>
       <c r="Q65" s="4" t="str">
-        <f>_xlfn.CONCAT(A65:B65,D65:H65)</f>
+        <f t="shared" ref="Q65:Q82" si="6">_xlfn.CONCAT(A65:B65,D65:H65)</f>
         <v/>
       </c>
       <c r="R65" s="8"/>
@@ -7664,7 +7664,7 @@
         <v>1015</v>
       </c>
       <c r="Q66" s="4" t="str">
-        <f>_xlfn.CONCAT(A66:B66,D66:H66)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic081mp</v>
       </c>
       <c r="R66" s="8" t="s">
@@ -7674,8 +7674,8 @@
         <v>728</v>
       </c>
       <c r="T66" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S66,"/mtr-rec/",O66)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7728,7 +7728,7 @@
         <v>1015</v>
       </c>
       <c r="Q67" s="4" t="str">
-        <f>_xlfn.CONCAT(A67:B67,D67:H67)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic082mp</v>
       </c>
       <c r="R67" s="8" t="s">
@@ -7738,8 +7738,8 @@
         <v>728</v>
       </c>
       <c r="T67" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S67,"/mtr-rec/",O67)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>1015</v>
       </c>
       <c r="Q68" s="4" t="str">
-        <f>_xlfn.CONCAT(A68:B68,D68:H68)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic083mp</v>
       </c>
       <c r="R68" s="8" t="s">
@@ -7802,8 +7802,8 @@
         <v>728</v>
       </c>
       <c r="T68" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S68,"/mtr-rec/",O68)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7856,7 +7856,7 @@
         <v>1015</v>
       </c>
       <c r="Q69" s="4" t="str">
-        <f>_xlfn.CONCAT(A69:B69,D69:H69)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic084mp</v>
       </c>
       <c r="R69" s="8" t="s">
@@ -7866,8 +7866,8 @@
         <v>728</v>
       </c>
       <c r="T69" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S69,"/mtr-rec/",O69)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7920,7 +7920,7 @@
         <v>1015</v>
       </c>
       <c r="Q70" s="4" t="str">
-        <f>_xlfn.CONCAT(A70:B70,D70:H70)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic085mp</v>
       </c>
       <c r="R70" s="8" t="s">
@@ -7930,8 +7930,8 @@
         <v>728</v>
       </c>
       <c r="T70" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S70,"/mtr-rec/",O70)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -7984,7 +7984,7 @@
         <v>1015</v>
       </c>
       <c r="Q71" s="4" t="str">
-        <f>_xlfn.CONCAT(A71:B71,D71:H71)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic086mp</v>
       </c>
       <c r="R71" s="8" t="s">
@@ -7994,8 +7994,8 @@
         <v>728</v>
       </c>
       <c r="T71" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S71,"/mtr-rec/",O71)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8048,7 +8048,7 @@
         <v>1015</v>
       </c>
       <c r="Q72" s="4" t="str">
-        <f>_xlfn.CONCAT(A72:B72,D72:H72)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic087mp</v>
       </c>
       <c r="R72" s="8" t="s">
@@ -8058,8 +8058,8 @@
         <v>728</v>
       </c>
       <c r="T72" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S72,"/mtr-rec/",O72)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu080mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm080</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8096,7 +8096,7 @@
         <v>1015</v>
       </c>
       <c r="Q73" s="4" t="str">
-        <f>_xlfn.CONCAT(A73:B73,D73:H73)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R73" s="8"/>
@@ -8153,7 +8153,7 @@
         <v>1016</v>
       </c>
       <c r="Q74" s="4" t="str">
-        <f>_xlfn.CONCAT(A74:B74,D74:H74)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic091mp</v>
       </c>
       <c r="R74" s="8" t="s">
@@ -8163,8 +8163,8 @@
         <v>728</v>
       </c>
       <c r="T74" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S74,"/mtr-rec/",O74)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8217,7 +8217,7 @@
         <v>1016</v>
       </c>
       <c r="Q75" s="4" t="str">
-        <f>_xlfn.CONCAT(A75:B75,D75:H75)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic092mp</v>
       </c>
       <c r="R75" s="8" t="s">
@@ -8227,8 +8227,8 @@
         <v>728</v>
       </c>
       <c r="T75" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S75,"/mtr-rec/",O75)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8281,7 +8281,7 @@
         <v>1016</v>
       </c>
       <c r="Q76" s="4" t="str">
-        <f>_xlfn.CONCAT(A76:B76,D76:H76)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic093mp</v>
       </c>
       <c r="R76" s="8" t="s">
@@ -8291,8 +8291,8 @@
         <v>728</v>
       </c>
       <c r="T76" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S76,"/mtr-rec/",O76)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8345,7 +8345,7 @@
         <v>1016</v>
       </c>
       <c r="Q77" s="4" t="str">
-        <f>_xlfn.CONCAT(A77:B77,D77:H77)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic094mp</v>
       </c>
       <c r="R77" s="8" t="s">
@@ -8355,8 +8355,8 @@
         <v>728</v>
       </c>
       <c r="T77" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S77,"/mtr-rec/",O77)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8409,7 +8409,7 @@
         <v>1016</v>
       </c>
       <c r="Q78" s="4" t="str">
-        <f>_xlfn.CONCAT(A78:B78,D78:H78)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic095mp</v>
       </c>
       <c r="R78" s="8" t="s">
@@ -8419,8 +8419,8 @@
         <v>728</v>
       </c>
       <c r="T78" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S78,"/mtr-rec/",O78)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
         <v>1016</v>
       </c>
       <c r="Q79" s="4" t="str">
-        <f>_xlfn.CONCAT(A79:B79,D79:H79)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic096mp</v>
       </c>
       <c r="R79" s="8" t="s">
@@ -8483,8 +8483,8 @@
         <v>728</v>
       </c>
       <c r="T79" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S79,"/mtr-rec/",O79)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8537,7 +8537,7 @@
         <v>1016</v>
       </c>
       <c r="Q80" s="4" t="str">
-        <f>_xlfn.CONCAT(A80:B80,D80:H80)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic097mp</v>
       </c>
       <c r="R80" s="8" t="s">
@@ -8547,8 +8547,8 @@
         <v>728</v>
       </c>
       <c r="T80" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S80,"/mtr-rec/",O80)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu090mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm090</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8585,7 +8585,7 @@
         <v>1016</v>
       </c>
       <c r="Q81" s="4" t="str">
-        <f>_xlfn.CONCAT(A81:B81,D81:H81)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R81" s="8"/>
@@ -8642,7 +8642,7 @@
         <v>1017</v>
       </c>
       <c r="Q82" s="4" t="str">
-        <f>_xlfn.CONCAT(A82:B82,D82:H82)</f>
+        <f t="shared" si="6"/>
         <v>tvsnvrpic101mp</v>
       </c>
       <c r="R82" s="8" t="s">
@@ -8652,8 +8652,8 @@
         <v>728</v>
       </c>
       <c r="T82" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S82,"/mtr-rec/",O82)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu100mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm100</v>
       </c>
     </row>
     <row r="83" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8770,8 +8770,8 @@
         <v>728</v>
       </c>
       <c r="T84" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S84,"/mtr-rec/",O84)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu110mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm110</v>
       </c>
     </row>
     <row r="85" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -8888,8 +8888,8 @@
         <v>728</v>
       </c>
       <c r="T86" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S86,"/mtr-rec/",O86)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu120mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm120</v>
       </c>
     </row>
     <row r="87" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9006,8 +9006,8 @@
         <v>728</v>
       </c>
       <c r="T88" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S88,"/mtr-rec/",O88)</f>
-        <v>/ifs/infstonas001mp/mtr-rec/tvsnvrclu130mp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001mp/mtr-rec/clnvrm130</v>
       </c>
     </row>
     <row r="89" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9124,8 +9124,8 @@
         <v>729</v>
       </c>
       <c r="T90" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S90,"/rtr-rec/",O90)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu100rp</v>
+        <f t="shared" si="4"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr100</v>
       </c>
     </row>
     <row r="91" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9242,8 +9242,8 @@
         <v>729</v>
       </c>
       <c r="T92" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S92,"/rtr-rec/",O92)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu110rp</v>
+        <f t="shared" ref="T92:T154" si="7">_xlfn.CONCAT("/ifs/",S92,"/mtr-rec/",P92)</f>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr110</v>
       </c>
     </row>
     <row r="93" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9360,8 +9360,8 @@
         <v>729</v>
       </c>
       <c r="T94" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S94,"/rtr-rec/",O94)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu120rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr120</v>
       </c>
     </row>
     <row r="95" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9478,8 +9478,8 @@
         <v>729</v>
       </c>
       <c r="T96" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S96,"/rtr-rec/",O96)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu130rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr130</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>1025</v>
       </c>
       <c r="Q98" s="4" t="str">
-        <f>_xlfn.CONCAT(A98:B98,D98:H98)</f>
+        <f t="shared" ref="Q98:Q129" si="8">_xlfn.CONCAT(A98:B98,D98:H98)</f>
         <v>tvsnvrpic001rp</v>
       </c>
       <c r="R98" s="10" t="s">
@@ -9596,8 +9596,8 @@
         <v>729</v>
       </c>
       <c r="T98" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S98,"/rtr-rec/",O98)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9650,7 +9650,7 @@
         <v>1025</v>
       </c>
       <c r="Q99" s="4" t="str">
-        <f>_xlfn.CONCAT(A99:B99,D99:H99)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic002rp</v>
       </c>
       <c r="R99" s="10" t="s">
@@ -9660,8 +9660,8 @@
         <v>729</v>
       </c>
       <c r="T99" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S99,"/rtr-rec/",O99)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9714,7 +9714,7 @@
         <v>1025</v>
       </c>
       <c r="Q100" s="4" t="str">
-        <f>_xlfn.CONCAT(A100:B100,D100:H100)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic003rp</v>
       </c>
       <c r="R100" s="10" t="s">
@@ -9724,8 +9724,8 @@
         <v>729</v>
       </c>
       <c r="T100" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S100,"/rtr-rec/",O100)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9778,7 +9778,7 @@
         <v>1025</v>
       </c>
       <c r="Q101" s="4" t="str">
-        <f>_xlfn.CONCAT(A101:B101,D101:H101)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic004rp</v>
       </c>
       <c r="R101" s="10" t="s">
@@ -9788,8 +9788,8 @@
         <v>729</v>
       </c>
       <c r="T101" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S101,"/rtr-rec/",O101)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9842,7 +9842,7 @@
         <v>1025</v>
       </c>
       <c r="Q102" s="4" t="str">
-        <f>_xlfn.CONCAT(A102:B102,D102:H102)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic005rp</v>
       </c>
       <c r="R102" s="10" t="s">
@@ -9852,8 +9852,8 @@
         <v>729</v>
       </c>
       <c r="T102" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S102,"/rtr-rec/",O102)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9906,7 +9906,7 @@
         <v>1025</v>
       </c>
       <c r="Q103" s="4" t="str">
-        <f>_xlfn.CONCAT(A103:B103,D103:H103)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic006rp</v>
       </c>
       <c r="R103" s="10" t="s">
@@ -9916,8 +9916,8 @@
         <v>729</v>
       </c>
       <c r="T103" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S103,"/rtr-rec/",O103)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -9970,7 +9970,7 @@
         <v>1025</v>
       </c>
       <c r="Q104" s="4" t="str">
-        <f>_xlfn.CONCAT(A104:B104,D104:H104)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic007rp</v>
       </c>
       <c r="R104" s="10" t="s">
@@ -9980,8 +9980,8 @@
         <v>729</v>
       </c>
       <c r="T104" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S104,"/rtr-rec/",O104)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu000rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr000</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10018,7 +10018,7 @@
         <v>1025</v>
       </c>
       <c r="Q105" s="4" t="str">
-        <f>_xlfn.CONCAT(A105:B105,D105:H105)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R105" s="10"/>
@@ -10075,7 +10075,7 @@
         <v>1026</v>
       </c>
       <c r="Q106" s="4" t="str">
-        <f>_xlfn.CONCAT(A106:B106,D106:H106)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic011rp</v>
       </c>
       <c r="R106" s="10" t="s">
@@ -10085,8 +10085,8 @@
         <v>729</v>
       </c>
       <c r="T106" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S106,"/rtr-rec/",O106)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10139,7 +10139,7 @@
         <v>1026</v>
       </c>
       <c r="Q107" s="4" t="str">
-        <f>_xlfn.CONCAT(A107:B107,D107:H107)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic012rp</v>
       </c>
       <c r="R107" s="10" t="s">
@@ -10149,8 +10149,8 @@
         <v>729</v>
       </c>
       <c r="T107" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S107,"/rtr-rec/",O107)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10203,7 +10203,7 @@
         <v>1026</v>
       </c>
       <c r="Q108" s="4" t="str">
-        <f>_xlfn.CONCAT(A108:B108,D108:H108)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic013rp</v>
       </c>
       <c r="R108" s="10" t="s">
@@ -10213,8 +10213,8 @@
         <v>729</v>
       </c>
       <c r="T108" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S108,"/rtr-rec/",O108)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10267,7 +10267,7 @@
         <v>1026</v>
       </c>
       <c r="Q109" s="4" t="str">
-        <f>_xlfn.CONCAT(A109:B109,D109:H109)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic014rp</v>
       </c>
       <c r="R109" s="10" t="s">
@@ -10277,8 +10277,8 @@
         <v>729</v>
       </c>
       <c r="T109" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S109,"/rtr-rec/",O109)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10331,7 +10331,7 @@
         <v>1026</v>
       </c>
       <c r="Q110" s="4" t="str">
-        <f>_xlfn.CONCAT(A110:B110,D110:H110)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic015rp</v>
       </c>
       <c r="R110" s="10" t="s">
@@ -10341,8 +10341,8 @@
         <v>729</v>
       </c>
       <c r="T110" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S110,"/rtr-rec/",O110)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10395,7 +10395,7 @@
         <v>1026</v>
       </c>
       <c r="Q111" s="4" t="str">
-        <f>_xlfn.CONCAT(A111:B111,D111:H111)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic016rp</v>
       </c>
       <c r="R111" s="10" t="s">
@@ -10405,8 +10405,8 @@
         <v>729</v>
       </c>
       <c r="T111" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S111,"/rtr-rec/",O111)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10459,7 +10459,7 @@
         <v>1026</v>
       </c>
       <c r="Q112" s="4" t="str">
-        <f>_xlfn.CONCAT(A112:B112,D112:H112)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic017rp</v>
       </c>
       <c r="R112" s="10" t="s">
@@ -10469,8 +10469,8 @@
         <v>729</v>
       </c>
       <c r="T112" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S112,"/rtr-rec/",O112)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu010rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr010</v>
       </c>
     </row>
     <row r="113" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10507,7 +10507,7 @@
         <v>1026</v>
       </c>
       <c r="Q113" s="4" t="str">
-        <f>_xlfn.CONCAT(A113:B113,D113:H113)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R113" s="10"/>
@@ -10564,7 +10564,7 @@
         <v>1027</v>
       </c>
       <c r="Q114" s="4" t="str">
-        <f>_xlfn.CONCAT(A114:B114,D114:H114)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic021rp</v>
       </c>
       <c r="R114" s="10" t="s">
@@ -10574,8 +10574,8 @@
         <v>729</v>
       </c>
       <c r="T114" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S114,"/rtr-rec/",O114)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="115" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10628,7 +10628,7 @@
         <v>1027</v>
       </c>
       <c r="Q115" s="4" t="str">
-        <f>_xlfn.CONCAT(A115:B115,D115:H115)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic022rp</v>
       </c>
       <c r="R115" s="10" t="s">
@@ -10638,8 +10638,8 @@
         <v>729</v>
       </c>
       <c r="T115" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S115,"/rtr-rec/",O115)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="116" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10692,7 +10692,7 @@
         <v>1027</v>
       </c>
       <c r="Q116" s="4" t="str">
-        <f>_xlfn.CONCAT(A116:B116,D116:H116)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic023rp</v>
       </c>
       <c r="R116" s="10" t="s">
@@ -10702,8 +10702,8 @@
         <v>729</v>
       </c>
       <c r="T116" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S116,"/rtr-rec/",O116)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="117" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10756,7 +10756,7 @@
         <v>1027</v>
       </c>
       <c r="Q117" s="4" t="str">
-        <f>_xlfn.CONCAT(A117:B117,D117:H117)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic024rp</v>
       </c>
       <c r="R117" s="10" t="s">
@@ -10766,8 +10766,8 @@
         <v>729</v>
       </c>
       <c r="T117" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S117,"/rtr-rec/",O117)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="118" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10820,7 +10820,7 @@
         <v>1027</v>
       </c>
       <c r="Q118" s="4" t="str">
-        <f>_xlfn.CONCAT(A118:B118,D118:H118)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic025rp</v>
       </c>
       <c r="R118" s="10" t="s">
@@ -10830,8 +10830,8 @@
         <v>729</v>
       </c>
       <c r="T118" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S118,"/rtr-rec/",O118)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="119" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10884,7 +10884,7 @@
         <v>1027</v>
       </c>
       <c r="Q119" s="4" t="str">
-        <f>_xlfn.CONCAT(A119:B119,D119:H119)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic026rp</v>
       </c>
       <c r="R119" s="10" t="s">
@@ -10894,8 +10894,8 @@
         <v>729</v>
       </c>
       <c r="T119" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S119,"/rtr-rec/",O119)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="120" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10948,7 +10948,7 @@
         <v>1027</v>
       </c>
       <c r="Q120" s="4" t="str">
-        <f>_xlfn.CONCAT(A120:B120,D120:H120)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic027rp</v>
       </c>
       <c r="R120" s="10" t="s">
@@ -10958,8 +10958,8 @@
         <v>729</v>
       </c>
       <c r="T120" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S120,"/rtr-rec/",O120)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu020rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr020</v>
       </c>
     </row>
     <row r="121" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -10996,7 +10996,7 @@
         <v>1027</v>
       </c>
       <c r="Q121" s="4" t="str">
-        <f>_xlfn.CONCAT(A121:B121,D121:H121)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R121" s="10"/>
@@ -11053,7 +11053,7 @@
         <v>1028</v>
       </c>
       <c r="Q122" s="4" t="str">
-        <f>_xlfn.CONCAT(A122:B122,D122:H122)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic031rp</v>
       </c>
       <c r="R122" s="10" t="s">
@@ -11063,8 +11063,8 @@
         <v>729</v>
       </c>
       <c r="T122" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S122,"/rtr-rec/",O122)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="123" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11117,7 +11117,7 @@
         <v>1028</v>
       </c>
       <c r="Q123" s="4" t="str">
-        <f>_xlfn.CONCAT(A123:B123,D123:H123)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic032rp</v>
       </c>
       <c r="R123" s="10" t="s">
@@ -11127,8 +11127,8 @@
         <v>729</v>
       </c>
       <c r="T123" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S123,"/rtr-rec/",O123)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="124" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11181,7 +11181,7 @@
         <v>1028</v>
       </c>
       <c r="Q124" s="4" t="str">
-        <f>_xlfn.CONCAT(A124:B124,D124:H124)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic033rp</v>
       </c>
       <c r="R124" s="10" t="s">
@@ -11191,8 +11191,8 @@
         <v>729</v>
       </c>
       <c r="T124" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S124,"/rtr-rec/",O124)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="125" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11245,7 +11245,7 @@
         <v>1028</v>
       </c>
       <c r="Q125" s="4" t="str">
-        <f>_xlfn.CONCAT(A125:B125,D125:H125)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic034rp</v>
       </c>
       <c r="R125" s="10" t="s">
@@ -11255,8 +11255,8 @@
         <v>729</v>
       </c>
       <c r="T125" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S125,"/rtr-rec/",O125)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="126" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11309,7 +11309,7 @@
         <v>1028</v>
       </c>
       <c r="Q126" s="4" t="str">
-        <f>_xlfn.CONCAT(A126:B126,D126:H126)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic035rp</v>
       </c>
       <c r="R126" s="10" t="s">
@@ -11319,8 +11319,8 @@
         <v>729</v>
       </c>
       <c r="T126" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S126,"/rtr-rec/",O126)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="127" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11373,7 +11373,7 @@
         <v>1028</v>
       </c>
       <c r="Q127" s="4" t="str">
-        <f>_xlfn.CONCAT(A127:B127,D127:H127)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic036rp</v>
       </c>
       <c r="R127" s="10" t="s">
@@ -11383,8 +11383,8 @@
         <v>729</v>
       </c>
       <c r="T127" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S127,"/rtr-rec/",O127)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="128" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11437,7 +11437,7 @@
         <v>1028</v>
       </c>
       <c r="Q128" s="4" t="str">
-        <f>_xlfn.CONCAT(A128:B128,D128:H128)</f>
+        <f t="shared" si="8"/>
         <v>tvsnvrpic037rp</v>
       </c>
       <c r="R128" s="10" t="s">
@@ -11447,8 +11447,8 @@
         <v>729</v>
       </c>
       <c r="T128" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S128,"/rtr-rec/",O128)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu030rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr030</v>
       </c>
     </row>
     <row r="129" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11485,7 +11485,7 @@
         <v>1028</v>
       </c>
       <c r="Q129" s="4" t="str">
-        <f>_xlfn.CONCAT(A129:B129,D129:H129)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R129" s="10"/>
@@ -11542,7 +11542,7 @@
         <v>1029</v>
       </c>
       <c r="Q130" s="4" t="str">
-        <f>_xlfn.CONCAT(A130:B130,D130:H130)</f>
+        <f t="shared" ref="Q130:Q161" si="9">_xlfn.CONCAT(A130:B130,D130:H130)</f>
         <v>tvsnvrpic041rp</v>
       </c>
       <c r="R130" s="10" t="s">
@@ -11552,8 +11552,8 @@
         <v>729</v>
       </c>
       <c r="T130" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S130,"/rtr-rec/",O130)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="131" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11606,7 +11606,7 @@
         <v>1029</v>
       </c>
       <c r="Q131" s="4" t="str">
-        <f>_xlfn.CONCAT(A131:B131,D131:H131)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic042rp</v>
       </c>
       <c r="R131" s="10" t="s">
@@ -11616,8 +11616,8 @@
         <v>729</v>
       </c>
       <c r="T131" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S131,"/rtr-rec/",O131)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="132" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11670,7 +11670,7 @@
         <v>1029</v>
       </c>
       <c r="Q132" s="4" t="str">
-        <f>_xlfn.CONCAT(A132:B132,D132:H132)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic043rp</v>
       </c>
       <c r="R132" s="10" t="s">
@@ -11680,8 +11680,8 @@
         <v>729</v>
       </c>
       <c r="T132" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S132,"/rtr-rec/",O132)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="133" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11734,7 +11734,7 @@
         <v>1029</v>
       </c>
       <c r="Q133" s="4" t="str">
-        <f>_xlfn.CONCAT(A133:B133,D133:H133)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic044rp</v>
       </c>
       <c r="R133" s="10" t="s">
@@ -11744,8 +11744,8 @@
         <v>729</v>
       </c>
       <c r="T133" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S133,"/rtr-rec/",O133)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="134" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11798,7 +11798,7 @@
         <v>1029</v>
       </c>
       <c r="Q134" s="4" t="str">
-        <f>_xlfn.CONCAT(A134:B134,D134:H134)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic045rp</v>
       </c>
       <c r="R134" s="10" t="s">
@@ -11808,8 +11808,8 @@
         <v>729</v>
       </c>
       <c r="T134" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S134,"/rtr-rec/",O134)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="135" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11862,7 +11862,7 @@
         <v>1029</v>
       </c>
       <c r="Q135" s="4" t="str">
-        <f>_xlfn.CONCAT(A135:B135,D135:H135)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic046rp</v>
       </c>
       <c r="R135" s="10" t="s">
@@ -11872,8 +11872,8 @@
         <v>729</v>
       </c>
       <c r="T135" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S135,"/rtr-rec/",O135)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="136" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11926,7 +11926,7 @@
         <v>1029</v>
       </c>
       <c r="Q136" s="4" t="str">
-        <f>_xlfn.CONCAT(A136:B136,D136:H136)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic047rp</v>
       </c>
       <c r="R136" s="10" t="s">
@@ -11936,8 +11936,8 @@
         <v>729</v>
       </c>
       <c r="T136" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S136,"/rtr-rec/",O136)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu040rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr040</v>
       </c>
     </row>
     <row r="137" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -11974,7 +11974,7 @@
         <v>1029</v>
       </c>
       <c r="Q137" s="4" t="str">
-        <f>_xlfn.CONCAT(A137:B137,D137:H137)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R137" s="10"/>
@@ -12031,7 +12031,7 @@
         <v>1030</v>
       </c>
       <c r="Q138" s="4" t="str">
-        <f>_xlfn.CONCAT(A138:B138,D138:H138)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic051rp</v>
       </c>
       <c r="R138" s="10" t="s">
@@ -12041,8 +12041,8 @@
         <v>729</v>
       </c>
       <c r="T138" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S138,"/rtr-rec/",O138)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="139" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12095,7 +12095,7 @@
         <v>1030</v>
       </c>
       <c r="Q139" s="4" t="str">
-        <f>_xlfn.CONCAT(A139:B139,D139:H139)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic052rp</v>
       </c>
       <c r="R139" s="10" t="s">
@@ -12105,8 +12105,8 @@
         <v>729</v>
       </c>
       <c r="T139" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S139,"/rtr-rec/",O139)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="140" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12159,7 +12159,7 @@
         <v>1030</v>
       </c>
       <c r="Q140" s="4" t="str">
-        <f>_xlfn.CONCAT(A140:B140,D140:H140)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic053rp</v>
       </c>
       <c r="R140" s="10" t="s">
@@ -12169,8 +12169,8 @@
         <v>729</v>
       </c>
       <c r="T140" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S140,"/rtr-rec/",O140)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="141" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12223,7 +12223,7 @@
         <v>1030</v>
       </c>
       <c r="Q141" s="4" t="str">
-        <f>_xlfn.CONCAT(A141:B141,D141:H141)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic054rp</v>
       </c>
       <c r="R141" s="10" t="s">
@@ -12233,8 +12233,8 @@
         <v>729</v>
       </c>
       <c r="T141" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S141,"/rtr-rec/",O141)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="142" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12287,7 +12287,7 @@
         <v>1030</v>
       </c>
       <c r="Q142" s="4" t="str">
-        <f>_xlfn.CONCAT(A142:B142,D142:H142)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic055rp</v>
       </c>
       <c r="R142" s="10" t="s">
@@ -12297,8 +12297,8 @@
         <v>729</v>
       </c>
       <c r="T142" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S142,"/rtr-rec/",O142)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="143" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12351,7 +12351,7 @@
         <v>1030</v>
       </c>
       <c r="Q143" s="4" t="str">
-        <f>_xlfn.CONCAT(A143:B143,D143:H143)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic056rp</v>
       </c>
       <c r="R143" s="10" t="s">
@@ -12361,8 +12361,8 @@
         <v>729</v>
       </c>
       <c r="T143" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S143,"/rtr-rec/",O143)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="144" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12415,7 +12415,7 @@
         <v>1030</v>
       </c>
       <c r="Q144" s="4" t="str">
-        <f>_xlfn.CONCAT(A144:B144,D144:H144)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic057rp</v>
       </c>
       <c r="R144" s="10" t="s">
@@ -12425,8 +12425,8 @@
         <v>729</v>
       </c>
       <c r="T144" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S144,"/rtr-rec/",O144)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu050rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr050</v>
       </c>
     </row>
     <row r="145" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12463,7 +12463,7 @@
         <v>1030</v>
       </c>
       <c r="Q145" s="4" t="str">
-        <f>_xlfn.CONCAT(A145:B145,D145:H145)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R145" s="10"/>
@@ -12520,7 +12520,7 @@
         <v>1031</v>
       </c>
       <c r="Q146" s="4" t="str">
-        <f>_xlfn.CONCAT(A146:B146,D146:H146)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic061rp</v>
       </c>
       <c r="R146" s="10" t="s">
@@ -12530,8 +12530,8 @@
         <v>729</v>
       </c>
       <c r="T146" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S146,"/rtr-rec/",O146)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="147" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12584,7 +12584,7 @@
         <v>1031</v>
       </c>
       <c r="Q147" s="4" t="str">
-        <f>_xlfn.CONCAT(A147:B147,D147:H147)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic062rp</v>
       </c>
       <c r="R147" s="10" t="s">
@@ -12594,8 +12594,8 @@
         <v>729</v>
       </c>
       <c r="T147" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S147,"/rtr-rec/",O147)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="148" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12648,7 +12648,7 @@
         <v>1031</v>
       </c>
       <c r="Q148" s="4" t="str">
-        <f>_xlfn.CONCAT(A148:B148,D148:H148)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic063rp</v>
       </c>
       <c r="R148" s="10" t="s">
@@ -12658,8 +12658,8 @@
         <v>729</v>
       </c>
       <c r="T148" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S148,"/rtr-rec/",O148)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="149" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12712,7 +12712,7 @@
         <v>1031</v>
       </c>
       <c r="Q149" s="4" t="str">
-        <f>_xlfn.CONCAT(A149:B149,D149:H149)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic064rp</v>
       </c>
       <c r="R149" s="10" t="s">
@@ -12722,8 +12722,8 @@
         <v>729</v>
       </c>
       <c r="T149" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S149,"/rtr-rec/",O149)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="150" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12776,7 +12776,7 @@
         <v>1031</v>
       </c>
       <c r="Q150" s="4" t="str">
-        <f>_xlfn.CONCAT(A150:B150,D150:H150)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic065rp</v>
       </c>
       <c r="R150" s="10" t="s">
@@ -12786,8 +12786,8 @@
         <v>729</v>
       </c>
       <c r="T150" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S150,"/rtr-rec/",O150)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="151" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12840,7 +12840,7 @@
         <v>1031</v>
       </c>
       <c r="Q151" s="4" t="str">
-        <f>_xlfn.CONCAT(A151:B151,D151:H151)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic066rp</v>
       </c>
       <c r="R151" s="10" t="s">
@@ -12850,8 +12850,8 @@
         <v>729</v>
       </c>
       <c r="T151" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S151,"/rtr-rec/",O151)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="152" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12904,7 +12904,7 @@
         <v>1031</v>
       </c>
       <c r="Q152" s="4" t="str">
-        <f>_xlfn.CONCAT(A152:B152,D152:H152)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic067rp</v>
       </c>
       <c r="R152" s="10" t="s">
@@ -12914,8 +12914,8 @@
         <v>729</v>
       </c>
       <c r="T152" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S152,"/rtr-rec/",O152)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu060rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr060</v>
       </c>
     </row>
     <row r="153" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -12952,7 +12952,7 @@
         <v>1031</v>
       </c>
       <c r="Q153" s="4" t="str">
-        <f>_xlfn.CONCAT(A153:B153,D153:H153)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R153" s="10"/>
@@ -13009,7 +13009,7 @@
         <v>1032</v>
       </c>
       <c r="Q154" s="4" t="str">
-        <f>_xlfn.CONCAT(A154:B154,D154:H154)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic071rp</v>
       </c>
       <c r="R154" s="10" t="s">
@@ -13019,8 +13019,8 @@
         <v>729</v>
       </c>
       <c r="T154" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S154,"/rtr-rec/",O154)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="7"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="155" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13073,7 +13073,7 @@
         <v>1032</v>
       </c>
       <c r="Q155" s="4" t="str">
-        <f>_xlfn.CONCAT(A155:B155,D155:H155)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic072rp</v>
       </c>
       <c r="R155" s="10" t="s">
@@ -13083,8 +13083,8 @@
         <v>729</v>
       </c>
       <c r="T155" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S155,"/rtr-rec/",O155)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" ref="T155:T176" si="10">_xlfn.CONCAT("/ifs/",S155,"/mtr-rec/",P155)</f>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="156" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13137,7 +13137,7 @@
         <v>1032</v>
       </c>
       <c r="Q156" s="4" t="str">
-        <f>_xlfn.CONCAT(A156:B156,D156:H156)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic073rp</v>
       </c>
       <c r="R156" s="10" t="s">
@@ -13147,8 +13147,8 @@
         <v>729</v>
       </c>
       <c r="T156" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S156,"/rtr-rec/",O156)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="157" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13201,7 +13201,7 @@
         <v>1032</v>
       </c>
       <c r="Q157" s="4" t="str">
-        <f>_xlfn.CONCAT(A157:B157,D157:H157)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic074rp</v>
       </c>
       <c r="R157" s="10" t="s">
@@ -13211,8 +13211,8 @@
         <v>729</v>
       </c>
       <c r="T157" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S157,"/rtr-rec/",O157)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="158" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13265,7 +13265,7 @@
         <v>1032</v>
       </c>
       <c r="Q158" s="4" t="str">
-        <f>_xlfn.CONCAT(A158:B158,D158:H158)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic075rp</v>
       </c>
       <c r="R158" s="10" t="s">
@@ -13275,8 +13275,8 @@
         <v>729</v>
       </c>
       <c r="T158" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S158,"/rtr-rec/",O158)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="159" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13329,7 +13329,7 @@
         <v>1032</v>
       </c>
       <c r="Q159" s="4" t="str">
-        <f>_xlfn.CONCAT(A159:B159,D159:H159)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic076rp</v>
       </c>
       <c r="R159" s="10" t="s">
@@ -13339,8 +13339,8 @@
         <v>729</v>
       </c>
       <c r="T159" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S159,"/rtr-rec/",O159)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="160" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13393,7 +13393,7 @@
         <v>1032</v>
       </c>
       <c r="Q160" s="4" t="str">
-        <f>_xlfn.CONCAT(A160:B160,D160:H160)</f>
+        <f t="shared" si="9"/>
         <v>tvsnvrpic077rp</v>
       </c>
       <c r="R160" s="10" t="s">
@@ -13403,8 +13403,8 @@
         <v>729</v>
       </c>
       <c r="T160" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S160,"/rtr-rec/",O160)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu070rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr070</v>
       </c>
     </row>
     <row r="161" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13441,7 +13441,7 @@
         <v>1032</v>
       </c>
       <c r="Q161" s="4" t="str">
-        <f>_xlfn.CONCAT(A161:B161,D161:H161)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R161" s="10"/>
@@ -13498,7 +13498,7 @@
         <v>1033</v>
       </c>
       <c r="Q162" s="4" t="str">
-        <f>_xlfn.CONCAT(A162:B162,D162:H162)</f>
+        <f t="shared" ref="Q162:Q177" si="11">_xlfn.CONCAT(A162:B162,D162:H162)</f>
         <v>tvsnvrpic081rp</v>
       </c>
       <c r="R162" s="10" t="s">
@@ -13508,8 +13508,8 @@
         <v>729</v>
       </c>
       <c r="T162" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S162,"/rtr-rec/",O162)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="163" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13562,7 +13562,7 @@
         <v>1033</v>
       </c>
       <c r="Q163" s="4" t="str">
-        <f>_xlfn.CONCAT(A163:B163,D163:H163)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic082rp</v>
       </c>
       <c r="R163" s="10" t="s">
@@ -13572,8 +13572,8 @@
         <v>729</v>
       </c>
       <c r="T163" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S163,"/rtr-rec/",O163)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="164" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13626,7 +13626,7 @@
         <v>1033</v>
       </c>
       <c r="Q164" s="4" t="str">
-        <f>_xlfn.CONCAT(A164:B164,D164:H164)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic083rp</v>
       </c>
       <c r="R164" s="10" t="s">
@@ -13636,8 +13636,8 @@
         <v>729</v>
       </c>
       <c r="T164" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S164,"/rtr-rec/",O164)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="165" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13690,7 +13690,7 @@
         <v>1033</v>
       </c>
       <c r="Q165" s="4" t="str">
-        <f>_xlfn.CONCAT(A165:B165,D165:H165)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic084rp</v>
       </c>
       <c r="R165" s="10" t="s">
@@ -13700,8 +13700,8 @@
         <v>729</v>
       </c>
       <c r="T165" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S165,"/rtr-rec/",O165)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="166" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13754,7 +13754,7 @@
         <v>1033</v>
       </c>
       <c r="Q166" s="4" t="str">
-        <f>_xlfn.CONCAT(A166:B166,D166:H166)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic085rp</v>
       </c>
       <c r="R166" s="10" t="s">
@@ -13764,8 +13764,8 @@
         <v>729</v>
       </c>
       <c r="T166" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S166,"/rtr-rec/",O166)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="167" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13818,7 +13818,7 @@
         <v>1033</v>
       </c>
       <c r="Q167" s="4" t="str">
-        <f>_xlfn.CONCAT(A167:B167,D167:H167)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic086rp</v>
       </c>
       <c r="R167" s="10" t="s">
@@ -13828,8 +13828,8 @@
         <v>729</v>
       </c>
       <c r="T167" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S167,"/rtr-rec/",O167)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="168" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13882,7 +13882,7 @@
         <v>1033</v>
       </c>
       <c r="Q168" s="4" t="str">
-        <f>_xlfn.CONCAT(A168:B168,D168:H168)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic087rp</v>
       </c>
       <c r="R168" s="10" t="s">
@@ -13892,8 +13892,8 @@
         <v>729</v>
       </c>
       <c r="T168" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S168,"/rtr-rec/",O168)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu080rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr080</v>
       </c>
     </row>
     <row r="169" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -13930,7 +13930,7 @@
         <v>1033</v>
       </c>
       <c r="Q169" s="4" t="str">
-        <f>_xlfn.CONCAT(A169:B169,D169:H169)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R169" s="10"/>
@@ -13987,7 +13987,7 @@
         <v>1034</v>
       </c>
       <c r="Q170" s="4" t="str">
-        <f>_xlfn.CONCAT(A170:B170,D170:H170)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic091rp</v>
       </c>
       <c r="R170" s="10" t="s">
@@ -13997,8 +13997,8 @@
         <v>729</v>
       </c>
       <c r="T170" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S170,"/rtr-rec/",O170)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="171" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14051,7 +14051,7 @@
         <v>1034</v>
       </c>
       <c r="Q171" s="4" t="str">
-        <f>_xlfn.CONCAT(A171:B171,D171:H171)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic092rp</v>
       </c>
       <c r="R171" s="10" t="s">
@@ -14061,8 +14061,8 @@
         <v>729</v>
       </c>
       <c r="T171" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S171,"/rtr-rec/",O171)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="172" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14115,7 +14115,7 @@
         <v>1034</v>
       </c>
       <c r="Q172" s="4" t="str">
-        <f>_xlfn.CONCAT(A172:B172,D172:H172)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic093rp</v>
       </c>
       <c r="R172" s="10" t="s">
@@ -14125,8 +14125,8 @@
         <v>729</v>
       </c>
       <c r="T172" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S172,"/rtr-rec/",O172)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="173" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14179,7 +14179,7 @@
         <v>1034</v>
       </c>
       <c r="Q173" s="4" t="str">
-        <f>_xlfn.CONCAT(A173:B173,D173:H173)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic094rp</v>
       </c>
       <c r="R173" s="10" t="s">
@@ -14189,8 +14189,8 @@
         <v>729</v>
       </c>
       <c r="T173" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S173,"/rtr-rec/",O173)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="174" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14243,7 +14243,7 @@
         <v>1034</v>
       </c>
       <c r="Q174" s="4" t="str">
-        <f>_xlfn.CONCAT(A174:B174,D174:H174)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic095rp</v>
       </c>
       <c r="R174" s="10" t="s">
@@ -14253,8 +14253,8 @@
         <v>729</v>
       </c>
       <c r="T174" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S174,"/rtr-rec/",O174)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="175" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14307,7 +14307,7 @@
         <v>1034</v>
       </c>
       <c r="Q175" s="4" t="str">
-        <f>_xlfn.CONCAT(A175:B175,D175:H175)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic096rp</v>
       </c>
       <c r="R175" s="10" t="s">
@@ -14317,8 +14317,8 @@
         <v>729</v>
       </c>
       <c r="T175" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S175,"/rtr-rec/",O175)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="176" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14371,7 +14371,7 @@
         <v>1034</v>
       </c>
       <c r="Q176" s="4" t="str">
-        <f>_xlfn.CONCAT(A176:B176,D176:H176)</f>
+        <f t="shared" si="11"/>
         <v>tvsnvrpic097rp</v>
       </c>
       <c r="R176" s="10" t="s">
@@ -14381,8 +14381,8 @@
         <v>729</v>
       </c>
       <c r="T176" s="8" t="str">
-        <f>_xlfn.CONCAT("/ifs/",S176,"/rtr-rec/",O176)</f>
-        <v>/ifs/infstonas001rp/rtr-rec/tvsnvrclu090rp</v>
+        <f t="shared" si="10"/>
+        <v>/ifs/infstonas001rp/mtr-rec/clnvrr090</v>
       </c>
     </row>
     <row r="177" spans="1:20" ht="14.4" x14ac:dyDescent="0.25">
@@ -14419,7 +14419,7 @@
         <v>1034</v>
       </c>
       <c r="Q177" s="4" t="str">
-        <f>_xlfn.CONCAT(A177:B177,D177:H177)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R177" s="10"/>
